--- a/pacjenci/ANTONI SAJDAK.xlsx
+++ b/pacjenci/ANTONI SAJDAK.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/ANTONI SAJDAK.xlsx
+++ b/pacjenci/ANTONI SAJDAK.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>09.08.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 100mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm - do oceny w badaniu USG.  Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Miernie aktywne metabolicznie węzły chłonne okna aortalno-płucnego, przytchawicze dolne prawe, we wnękach obu płuc oraz oskrzelowo-płucne prawe wielkości do 14mm, SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlane pobudzenie metaboliczne w topografii żołądka i części dwunastnicy, SUV max do 5,1, bez wyodrębniających się obszarów jednoznacznie zwiększonego metabolizmu FDG [w przeglądowym badaniu TK zwraca uwagę wyraźne pogrubienie fałdów żołądkowych - do kontroli endoskopowej. Odcinkowe pobudzenie metaboliczne w jelitach-czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klisy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Drobne zwapnienia w wyraźnie powiększonej prostacie - do  kontroli urologicznej.   Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności idyskopatie w odcinku szyjnym kręgosłupa. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach zebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność miernie aktywnych metabolicznie węzłów chłonnych środpiersia i KLP. Rozlane pobudzenie metaboliczne w topografii żołądka i części dwunastnicy, bez wyodrębniających się obszarów jednoznacznie zwiększonego metabolizmu FDG - do kontroli endoskopowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>5.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>23.12.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Ocena remisji choroby po 3 cyklach immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 89 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm - do oceny w badaniu USG.  Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlane pobudzenie metaboliczne w topografii żołądka SUV max do 4,2 [w przeglądowym badaniu TK zwraca uwagę wyraźne pogrubienie fałdów żołądkowych - do kontroli endoskopowej. Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Drobne zwapnienia w wyraźnie powiększonej prostacie - do  kontroli urologicznej.   Układ kostny: Rozlanie wzmożony metabolizm FDG w całym układzie kostnym objętym badaniem SUV max do 8,1- w pierwszej kolejności związany z prowadzonym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 3,1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozlanie wzmożony metabolizm FDG w całym układzie kostnym objętym badaniem - w pierwszej kolejności związany z prowadzonym leczeniem. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>8.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>04.04.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Ocena remisji choroby po zakończeniu immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 112mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm, SUV max 3,0 - do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: - przytchawiczy dolny prawy i wnęki płuca prawego wielkości do 12mm wg PET, SUV max do 4,6. Niewykluczona obecność drobnych węzłów chłonnych przy tętnicy płucnej lewej, oskrzelowo-płucnych lewych, SUV max do 3,7- do oceny w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste [z wydatnymi pęcherzami rozedmowymi] w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego, z wydatnymi pęcherzami rozedmowymi oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w powiększonej prostacie ze zwapnieniami, SUV max do 3,7 - do kontroli urologicznej. Zwiekszony metabolizm FDG w bańce odbytu - fizjologicznie? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek.   Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa.  Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3.  Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne:  Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nielicznych pobudzonych metaboliczne węzłów chłonnych w KLP- do weryfikacji/ kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>06.12.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 104mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 32x18mm - opisywana już poprzednio - aktualnie progresja wielkości. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Miernie pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy i wnęki płuca prawego, wielkości do 11mm wg PET, SUV max do 2,8- do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste [z wydatnymi pęcherzami rozedmowymi] w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego, z wydatnymi pęcherzami rozedmowymi, także podostrogowo oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Nieaktywne metabolicznie węzły chłonne przytchawicze i okna aortalno-płucnego wielkości do 11mm.   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w powiększonej prostacie ze zwapnieniami- opisywane już poprzednio. Zwiekszony metabolizm FDG w topografii odbytu - fizjologicznie? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek.   Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa.  Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Wklęsłe obrysy blaszek granicznych trzonów kręgowych: L3, L4 i L5. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3.  Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne:  Nasilona miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2.8</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ANTONI SAJDAK.xlsx
+++ b/pacjenci/ANTONI SAJDAK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 100mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm - do oceny w badaniu USG.  Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Miernie aktywne metabolicznie węzły chłonne okna aortalno-płucnego, przytchawicze dolne prawe, we wnękach obu płuc oraz oskrzelowo-płucne prawe wielkości do 14mm, SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlane pobudzenie metaboliczne w topografii żołądka i części dwunastnicy, SUV max do 5,1, bez wyodrębniających się obszarów jednoznacznie zwiększonego metabolizmu FDG [w przeglądowym badaniu TK zwraca uwagę wyraźne pogrubienie fałdów żołądkowych - do kontroli endoskopowej. Odcinkowe pobudzenie metaboliczne w jelitach-czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klisy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Drobne zwapnienia w wyraźnie powiększonej prostacie - do  kontroli urologicznej.   Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności idyskopatie w odcinku szyjnym kręgosłupa. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach zebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm - do oceny w badaniu USG.  Drobne nieaktywne metabolicznie węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Miernie aktywne metabolicznie węzły chłonne okna aortalno-płucnego, przytchawicze dolne prawe, we wnękach obu płuc oraz oskrzelowo-płucne prawe wielkości do 14mm, SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rozlane pobudzenie metaboliczne w topografii żołądka i części dwunastnicy, SUV max do 5,1, bez wyodrębniających się obszarów jednoznacznie zwiększonego metabolizmu FDG [w przeglądowym badaniu TK zwraca uwagę wyraźne pogrubienie fałdów żołądkowych - do kontroli endoskopowej. Odcinkowe pobudzenie metaboliczne w jelitach-czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klisy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Drobne zwapnienia w wyraźnie powiększonej prostacie - do  kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności idyskopatie w odcinku szyjnym kręgosłupa. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach zebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne: Miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność miernie aktywnych metabolicznie węzłów chłonnych środpiersia i KLP. Rozlane pobudzenie metaboliczne w topografii żołądka i części dwunastnicy, bez wyodrębniających się obszarów jednoznacznie zwiększonego metabolizmu FDG - do kontroli endoskopowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 89 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm - do oceny w badaniu USG.  Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlane pobudzenie metaboliczne w topografii żołądka SUV max do 4,2 [w przeglądowym badaniu TK zwraca uwagę wyraźne pogrubienie fałdów żołądkowych - do kontroli endoskopowej. Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Drobne zwapnienia w wyraźnie powiększonej prostacie - do  kontroli urologicznej.   Układ kostny: Rozlanie wzmożony metabolizm FDG w całym układzie kostnym objętym badaniem SUV max do 8,1- w pierwszej kolejności związany z prowadzonym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 3,1</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm - do oceny w badaniu USG.  Drobne nieaktywne metabolicznie węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlane pobudzenie metaboliczne w topografii żołądka SUV max do 4,2 [w przeglądowym badaniu TK zwraca uwagę wyraźne pogrubienie fałdów żołądkowych - do kontroli endoskopowej. Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Drobne zwapnienia w wyraźnie powiększonej prostacie - do  kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w całym układzie kostnym objętym badaniem SUV max do 8,1- w pierwszej kolejności związany z prowadzonym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne: Miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozlanie wzmożony metabolizm FDG w całym układzie kostnym objętym badaniem - w pierwszej kolejności związany z prowadzonym leczeniem. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>8.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 112mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm, SUV max 3,0 - do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: - przytchawiczy dolny prawy i wnęki płuca prawego wielkości do 12mm wg PET, SUV max do 4,6. Niewykluczona obecność drobnych węzłów chłonnych przy tętnicy płucnej lewej, oskrzelowo-płucnych lewych, SUV max do 3,7- do oceny w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste [z wydatnymi pęcherzami rozedmowymi] w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego, z wydatnymi pęcherzami rozedmowymi oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w powiększonej prostacie ze zwapnieniami, SUV max do 3,7 - do kontroli urologicznej. Zwiekszony metabolizm FDG w bańce odbytu - fizjologicznie? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek.   Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa.  Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3.  Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne:  Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,6</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 25x18mm, SUV max 3,0 - do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Drobne nieaktywne metabolicznie węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne: - przytchawiczy dolny prawy i wnęki płuca prawego wielkości do 12mm wg PET, SUV max do 4,6. Niewykluczona obecność drobnych węzłów chłonnych przy tętnicy płucnej lewej, oskrzelowo-płucnych lewych, SUV max do 3,7- do oceny w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste [z wydatnymi pęcherzami rozedmowymi] w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego, z wydatnymi pęcherzami rozedmowymi oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w powiększonej prostacie ze zwapnieniami, SUV max do 3,7 - do kontroli urologicznej. Zwiekszony metabolizm FDG w bańce odbytu - fizjologicznie? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa.  Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3.  Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne:  Miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nielicznych pobudzonych metaboliczne węzłów chłonnych w KLP- do weryfikacji/ kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 104mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 32x18mm - opisywana już poprzednio - aktualnie progresja wielkości. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Drobne nieaktywne metabolicznie węzły chłonne szyjne.   Klatka piersiowa i śródpiersie: Miernie pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy i wnęki płuca prawego, wielkości do 11mm wg PET, SUV max do 2,8- do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste [z wydatnymi pęcherzami rozedmowymi] w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego, z wydatnymi pęcherzami rozedmowymi, także podostrogowo oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Nieaktywne metabolicznie węzły chłonne przytchawicze i okna aortalno-płucnego wielkości do 11mm.   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w powiększonej prostacie ze zwapnieniami- opisywane już poprzednio. Zwiekszony metabolizm FDG w topografii odbytu - fizjologicznie? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek.   Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa.  Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Wklęsłe obrysy blaszek granicznych trzonów kręgowych: L3, L4 i L5. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3.  Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne:  Nasilona miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK ze zwapnieniami, powiększona w zakresie lewego płata, schodzącego do śródpiersia po stronie lewej, z wyodrębniającą się w jego części grzbietowej hypodensyjną zmianą, wielkości ok. 32x18mm - opisywana już poprzednio - aktualnie progresja wielkości. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej. Niewielkie zgrubienia błony śluzowej u podstawy lewej zatoki czołowej. Niewielkie przyścienne i polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej. Drobne nieaktywne metabolicznie węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Miernie pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy i wnęki płuca prawego, wielkości do 11mm wg PET, SUV max do 2,8- do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nasilone zmiany rozedmowo-włókniste [z wydatnymi pęcherzami rozedmowymi] w szczytach obu płuc, z drobnymi zwapnieniami. Wydatne zmiany rozedmowe w płacie górnym płuca prawego, z wydatnymi pęcherzami rozedmowymi, także podostrogowo oraz mniej nasilone lewego. Niewielkie grubościenne pęcherze rozedmowe obwodowo w segm. 3/6 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Nieaktywne metabolicznie węzły chłonne przytchawicze i okna aortalno-płucnego wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w powiększonej prostacie ze zwapnieniami- opisywane już poprzednio. Zwiekszony metabolizm FDG w topografii odbytu - fizjologicznie? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwapnienia/klipsy naczyniowe w nadbrzuszu, lewobocznie od linii pośrodkowej ciała. Drobne uwapnione konkrementy w pęcherzyku żółciowym. Cechy wydatnej lipofibromatozy we wnękach obu nerek.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa.  Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Wklęsłe obrysy blaszek granicznych trzonów kręgowych: L3, L4 i L5. Pojedynczy wydatny guzek Schmorla w obrębie blaszki granicznej górnej trzonu L3.  Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych [wydatne w odcinku szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie lewej kości udowej oraz wydatna w głowie prawej kości udowej.   Inne:  Nasilona miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>2.8</v>
       </c>
     </row>
